--- a/Documents/Client Shared Files/Delivery_Wireless_Battery_Charger_19thMarch2022/BOM/Wirless Battery Charger_BOM_19thMarch2022.xlsx
+++ b/Documents/Client Shared Files/Delivery_Wireless_Battery_Charger_19thMarch2022/BOM/Wirless Battery Charger_BOM_19thMarch2022.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="25225"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usman\Dropbox\DARKT\BQ51013B 15-FEB-2022\Delivery_Wireless_Battery_Charger_19thMarch2022\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\DarkTag-PCBReview\Documents\Client Shared Files\Delivery_Wireless_Battery_Charger_19thMarch2022\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CACF004-BAC0-4A30-8DE6-C374B79862AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="2370" windowHeight="105"/>
+    <workbookView xWindow="-3960" yWindow="2895" windowWidth="11790" windowHeight="15360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Wirless Battery Charger_BOM_19t" sheetId="1" r:id="rId1"/>
@@ -17,10 +18,18 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Wirless Battery Charger_BOM_19t'!$1:$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -314,8 +323,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -323,8 +332,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,6 +350,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD3D3D3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,12 +387,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,7 +677,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -679,182 +706,182 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="7">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="1">
-        <v>1</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="7">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="1">
+      <c r="E4" s="7">
         <v>4</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="7">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="D6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="7">
         <v>2</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="D7" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="7">
         <v>2</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E8" s="7">
         <v>3</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="6" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="E9" s="7">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="D10" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="7">
         <v>2</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="6" t="s">
         <v>27</v>
       </c>
     </row>
@@ -865,16 +892,16 @@
       <c r="B11" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="9">
+        <v>1</v>
+      </c>
+      <c r="F11" s="8" t="s">
         <v>29</v>
       </c>
     </row>
@@ -885,56 +912,56 @@
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="9">
+        <v>1</v>
+      </c>
+      <c r="F12" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="D13" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="7">
         <v>2</v>
       </c>
-      <c r="F13" s="2" t="s">
+      <c r="F13" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="7">
         <v>2</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="7"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
@@ -943,7 +970,7 @@
       <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>40</v>
       </c>
       <c r="D15" s="2" t="s">
@@ -961,7 +988,7 @@
       <c r="B16" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D16" s="2" t="s">
@@ -975,22 +1002,22 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="E17" s="7">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -1001,7 +1028,7 @@
       <c r="B18" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="5" t="s">
         <v>50</v>
       </c>
       <c r="D18" s="2" t="s">
@@ -1013,58 +1040,58 @@
       <c r="F18" s="1"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="B19" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1"/>
+      <c r="E19" s="7">
+        <v>1</v>
+      </c>
+      <c r="F19" s="7"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1"/>
+      <c r="E20" s="7">
+        <v>1</v>
+      </c>
+      <c r="F20" s="7"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E21" s="1">
+      <c r="E21" s="7">
         <v>2</v>
       </c>
-      <c r="F21" s="1"/>
+      <c r="F21" s="7"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
@@ -1073,7 +1100,7 @@
       <c r="B22" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="5" t="s">
         <v>64</v>
       </c>
       <c r="D22" s="2" t="s">
@@ -1093,7 +1120,7 @@
       <c r="B23" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="5" t="s">
         <v>67</v>
       </c>
       <c r="D23" s="2" t="s">
@@ -1113,7 +1140,7 @@
       <c r="B24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="5" t="s">
         <v>69</v>
       </c>
       <c r="D24" s="2" t="s">
@@ -1133,7 +1160,7 @@
       <c r="B25" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="5" t="s">
         <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
@@ -1153,7 +1180,7 @@
       <c r="B26" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="5" t="s">
         <v>73</v>
       </c>
       <c r="D26" s="2" t="s">
@@ -1173,7 +1200,7 @@
       <c r="B27" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="5" t="s">
         <v>75</v>
       </c>
       <c r="D27" s="2" t="s">
@@ -1193,7 +1220,7 @@
       <c r="B28" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="5" t="s">
         <v>77</v>
       </c>
       <c r="D28" s="2" t="s">
@@ -1213,7 +1240,7 @@
       <c r="B29" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="5" t="s">
         <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
@@ -1233,7 +1260,7 @@
       <c r="B30" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="5" t="s">
         <v>81</v>
       </c>
       <c r="D30" s="2" t="s">
@@ -1253,7 +1280,7 @@
       <c r="B31" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="5" t="s">
         <v>83</v>
       </c>
       <c r="D31" s="2" t="s">
@@ -1273,7 +1300,7 @@
       <c r="B32" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="5" t="s">
         <v>86</v>
       </c>
       <c r="D32" s="2" t="s">
@@ -1291,7 +1318,7 @@
       <c r="B33" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="5" t="s">
         <v>89</v>
       </c>
       <c r="D33" s="2" t="s">
@@ -1311,7 +1338,7 @@
       <c r="B34" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="5" t="s">
         <v>92</v>
       </c>
       <c r="D34" s="2" t="s">
